--- a/Config/Excel/GameConfig/BuffGroupConfig.xlsx
+++ b/Config/Excel/GameConfig/BuffGroupConfig.xlsx
@@ -1,255 +1,177 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15320"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="17260" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="SkillEffectGroupConfig" sheetId="1" r:id="rId1"/>
+    <sheet name="BuffGroupConfig" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
-  <si>
-    <t>##var</t>
-  </si>
-  <si>
-    <t>Id</t>
-  </si>
-  <si>
-    <t>EffectIds</t>
-  </si>
-  <si>
-    <t>ExecMode</t>
-  </si>
-  <si>
-    <t>Desc</t>
-  </si>
-  <si>
-    <t>##type</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>array,int#sep=,</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>##</t>
-  </si>
-  <si>
-    <t>效果组ID</t>
-  </si>
-  <si>
-    <t>效果ID列表</t>
-  </si>
-  <si>
-    <t>执行方式</t>
-  </si>
-  <si>
-    <t>描述</t>
-  </si>
-  <si>
-    <t>玩家普攻效果组（割草增强）</t>
-  </si>
-  <si>
-    <t>怪物普攻效果组</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="21">
-    <font>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="20">
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <color theme="1"/>
       <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -550,154 +472,154 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -751,11 +673,74 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1042,96 +1027,762 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="4" outlineLevelCol="4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E40"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col min="3" max="3" width="26.7596153846154" customWidth="1"/>
-    <col min="4" max="4" width="45.6730769230769" customWidth="1"/>
+    <col width="47.75" customWidth="1" min="3" max="3"/>
+    <col width="45.6730769230769" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="B4">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>BuffIds</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>ExecMode</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Desc</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>(array#sep=,),int#ref=BuffConfigCategory</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Buff组ID</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>BuffID列表</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>执行方式</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>描述</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="n">
         <v>61001</v>
       </c>
-      <c r="C4" s="1">
-        <v>51011</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="B5">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>51011,53001</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>玩家普攻（伤害+击退1米）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="n">
         <v>61002</v>
       </c>
-      <c r="C5" s="1">
-        <v>51001</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5" t="s">
-        <v>15</v>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>51001,52001</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>怪物普攻+冻结0.5秒</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="n">
+        <v>61003</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>51011,55001</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>伤害+眩晕0.5秒</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="n">
+        <v>61004</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>51011,56001</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>伤害+减速30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="n">
+        <v>61005</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>51011,511001</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>伤害+毒伤DOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>61006</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>51011,53001,55001</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>伤害+击退1米+眩晕0.5秒</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="n">
+        <v>61007</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>51011,53002,55002</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>伤害+击退2米+眩晕1秒</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="n">
+        <v>61008</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>51011,56002</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>伤害+减速50%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>61009</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>51011,52002</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>伤害+冻结1秒</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>61010</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>51011,57001</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>伤害+吸血</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="n">
+        <v>61011</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>51011,59001</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>伤害+增攻50</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="n">
+        <v>61012</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>51011,510001</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>伤害+增防30</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="n">
+        <v>61013</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>51011,59001,510001</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>伤害+增攻50+增防30</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="n">
+        <v>61014</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>51011,59002,56002</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>伤害+增攻100+减速50%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="n">
+        <v>61015</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>51011,58001</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>伤害+护盾200</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="n">
+        <v>61016</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>51011,511002</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>伤害+猛毒DOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="n">
+        <v>61017</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>51011,52001,56001</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>伤害+冻结0.5秒+减速30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="n">
+        <v>61018</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>51011,55002,53002</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>伤害+眩晕1秒+击退2米</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="n">
+        <v>61019</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>51001,511002</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Boss普攻+猛毒DOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="n">
+        <v>61020</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>51001,52002</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Boss普攻+冻结1秒</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="n">
+        <v>61021</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>51001,56001</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Boss普攻+减速30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="n">
+        <v>61022</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>51001,55002</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Boss普攻+眩晕1秒</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="n">
+        <v>61023</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>51001,511002,56001</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Boss普攻+猛毒+减速30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="n">
+        <v>61024</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>54001,58001</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>治疗100+护盾200</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="n">
+        <v>61025</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>54002,58002,59001</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>治疗200+护盾500+增攻50</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="n">
+        <v>61026</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>54003</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>强力治疗500</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="n">
+        <v>61027</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>57001,57002</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>吸血+强化吸血</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="n">
+        <v>61028</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>51011,52003</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>伤害+冻结1.5秒</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="n">
+        <v>61029</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>51011,52004</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>伤害+冻结2秒</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="n">
+        <v>61030</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>51011,53003</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>伤害+击退3米</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="n">
+        <v>61031</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>51011,52005,56003</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>伤害+冻结3秒+减速70%</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="n">
+        <v>61032</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>51011,57002</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>伤害+强化吸血</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="n">
+        <v>61033</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>54003,58003</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>强力治疗500+护盾1000</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37"/>
+      <c r="B37">
+        <v>61101</v>
+      </c>
+      <c r="C37">
+        <v>53001</v>
+      </c>
+      <c r="D37">
+        <v>1</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>纯击退1米</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38"/>
+      <c r="B38">
+        <v>61102</v>
+      </c>
+      <c r="C38">
+        <v>52001</v>
+      </c>
+      <c r="D38">
+        <v>1</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>纯冻结0.5秒</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39"/>
+      <c r="B39">
+        <v>61103</v>
+      </c>
+      <c r="C39">
+        <v>56001</v>
+      </c>
+      <c r="D39">
+        <v>1</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>纯减速30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40"/>
+      <c r="B40">
+        <v>61104</v>
+      </c>
+      <c r="C40">
+        <v>511001</v>
+      </c>
+      <c r="D40">
+        <v>1</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>纯毒伤DOT</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>